--- a/stories/arbres/TREE-DIF-039.xlsx
+++ b/stories/arbres/TREE-DIF-039.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Adam est avec papa, sur le chemin de l'école. Adam a envie de jouer. papa est là, tout près. On va apprendre : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam écoute papa. Adam entend les mots : énergie, pas une faute, jouer ou attendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam respire. Adam retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de la cuisine, le livre et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam respire. Adam retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le jardin, le livre et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On se tait une seconde. papa dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On se tait une seconde.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam respire. Adam retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la chambre, les cubes et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la chambre, le livre et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la chambre, la dînette et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-039.xlsx
+++ b/stories/arbres/TREE-DIF-039.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Adam est avec papa, sur le chemin de l'école. Adam a envie de jouer. papa est là, tout près. On va apprendre : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam écoute papa. Adam entend les mots : énergie, pas une faute, jouer ou attendre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam respire. Adam retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Adam a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Adam rejoint le matin. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Adam rejoint après la sieste. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Adam rejoint le soir. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Adam a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de la cuisine, le livre et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Adam a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Adam rejoint le soir. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam respire. Adam retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Adam a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Adam rejoint le matin. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Adam rejoint après la sieste. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Adam rejoint le soir. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Adam a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le jardin, le livre et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Adam rejoint le soir. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9962,7 @@
           <t>narrateur|Adam a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10154,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10322,7 @@
           <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10658,7 @@
           <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10994,7 @@
           <t>narrateur|Adam rejoint le soir. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam respire. Adam retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Adam a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Adam rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Adam rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la chambre, les cubes et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Adam rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Adam a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Adam rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Adam rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la chambre, le livre et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Adam rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Adam a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam répète tout bas : énergie, pas une faute, jouer ou attendre. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Adam rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le matin. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Adam rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la chambre, la dînette et après la sieste. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Adam rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le soir. Adam a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Adam a entendu : énergie, pas une faute, jouer ou attendre. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-039.xlsx
+++ b/stories/arbres/TREE-DIF-039.xlsx
@@ -6923,12 +6923,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Sur le dos. Oui. Le sac à pois tient une ombre ronde. Je vois les pois ! Ne le lance pas encore. Aniss a les cheveux tout courts. Une mèche saute quand il respire. Ça sent déjà le trottoir chaud. Vos mains, sur le sac ? Oui, papa.</t>
+          <t>Sur le dos. Oui. Le sac à pois tient une ombre ronde. Je vois les pois ! On le garde pour le portail. Aniss a les cheveux tout courts. Une mèche saute quand il respire. Ça sent déjà le trottoir chaud. Vos mains, sur le sac ? Oui, papa.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Sur le dos. Oui. Le sac à pois tient une ombre ronde. Je vois les pois ! Ne le lance pas encore. Aniss a les cheveux tout courts. Une mèche saute quand il respire. Ça sent déjà le trottoir chaud. Vos mains, sur le sac ? Oui, papa.</t>
+          <t>Sur le dos. Oui. Le sac à pois tient une ombre ronde. Je vois les pois ! On le garde pour le portail. Aniss a les cheveux tout courts. Une mèche saute quand il respire. Ça sent déjà le trottoir chaud. Vos mains, sur le sac ? Oui, papa.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
 papa|Oui.
 narrateur|Le sac à pois tient une ombre ronde.
 copain|Je vois les pois !
-enfant-m|Ne le lance pas encore.
+enfant-m|On le garde pour le portail.
 narrateur|Aniss a les cheveux tout courts.
 narrateur|Une mèche saute quand il respire.
 maman|Ça sent déjà le trottoir chaud.
@@ -10134,12 +10134,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Le sac à pois fait un rond sur le muret. Ici, ça mène au portail, Aniss. Je vais plus loin, encore ! Le muret renvoie chaque pas, tout fort. Aniss court après le sac, plus loin. Le sac à pois attend au bord, un peu seule. Son élan remplit tout le mur. Toi tu vas plus loin, lui plus vite. On rebondit comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Le sac à pois s'appuie contre le muret. Ici, ça mène au portail, Aniss. Je vais plus loin, encore ! Le muret renvoie chaque pas, tout fort. Aniss court après le sac, plus loin. Le sac à pois attend au bord, un peu seule. Son élan remplit tout le mur. Toi tu vas plus loin, lui plus vite. On rebondit comment, alors ? Vous trouvez, tous les deux ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Le sac à pois fait un rond sur le muret. Ici, ça mène au portail, Aniss. Je vais plus loin, encore ! Le muret renvoie chaque pas, tout fort. Aniss court après le sac, plus loin. Le sac à pois attend au bord, un peu seule. Son élan remplit tout le mur. Toi tu vas plus loin, lui plus vite. On rebondit comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Le sac à pois s'appuie contre le muret. Ici, ça mène au portail, Aniss. Je vais plus loin, encore ! Le muret renvoie chaque pas, tout fort. Aniss court après le sac, plus loin. Le sac à pois attend au bord, un peu seule. Son élan remplit tout le mur. Toi tu vas plus loin, lui plus vite. On rebondit comment, alors ? Vous trouvez, tous les deux ?</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -10274,7 +10274,7 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Le sac à pois fait un rond sur le muret.
+          <t>narrateur|Le sac à pois s'appuie contre le muret.
 enfant-m|Ici, ça mène au portail, Aniss.
 copain|Je vais plus loin, encore !
 narrateur|Le muret renvoie chaque pas, tout fort.
@@ -15125,12 +15125,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La gourde bleue pose un pied près du muret. Ici, ça mène au portail, Aniss. Je vais plus loin, encore ! Le muret renvoie chaque pas, tout fort. Aniss chasse la gourde, le muret le suit. La gourde bleue attend au bord, un peu seule. Son élan remplit tout le mur. Toi tu vas plus loin, lui plus vite. On rebondit comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>La gourde bleue s'arrête près du muret. Ici, ça mène au portail, Aniss. Je vais plus loin, encore ! Le muret renvoie chaque pas, tout fort. Aniss court, la gourde reste contre la pierre. La gourde bleue attend au bord, un peu seule. Son élan remplit tout le mur. Toi tu vas plus loin, lui plus vite. On rebondit comment, alors ? Vous trouvez, tous les deux ?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>La gourde bleue pose un pied près du muret. Ici, ça mène au portail, Aniss. Je vais plus loin, encore ! Le muret renvoie chaque pas, tout fort. Aniss chasse la gourde, le muret le suit. La gourde bleue attend au bord, un peu seule. Son élan remplit tout le mur. Toi tu vas plus loin, lui plus vite. On rebondit comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>La gourde bleue s'arrête près du muret. Ici, ça mène au portail, Aniss. Je vais plus loin, encore ! Le muret renvoie chaque pas, tout fort. Aniss court, la gourde reste contre la pierre. La gourde bleue attend au bord, un peu seule. Son élan remplit tout le mur. Toi tu vas plus loin, lui plus vite. On rebondit comment, alors ? Vous trouvez, tous les deux ?</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -15265,11 +15265,11 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|La gourde bleue pose un pied près du muret.
+          <t>narrateur|La gourde bleue s'arrête près du muret.
 enfant-m|Ici, ça mène au portail, Aniss.
 copain|Je vais plus loin, encore !
 narrateur|Le muret renvoie chaque pas, tout fort.
-narrateur|Aniss chasse la gourde, le muret le suit.
+narrateur|Aniss court, la gourde reste contre la pierre.
 narrateur|La gourde bleue attend au bord, un peu seule.
 maman|Son élan remplit tout le mur.
 papa|Toi tu vas plus loin, lui plus vite.
@@ -16537,7 +16537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16580,6 +16580,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
